--- a/artfynd/A 31577-2025 artfynd.xlsx
+++ b/artfynd/A 31577-2025 artfynd.xlsx
@@ -675,73 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94158600</v>
+        <v>117770887</v>
       </c>
       <c r="B2" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Runmarö, Upl</t>
+          <t>Hemträsket, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716241.4694755387</v>
+        <v>716252</v>
       </c>
       <c r="R2" t="n">
-        <v>6578274.566415905</v>
+        <v>6578277</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-05</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-05</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,34 +768,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Björndahl</t>
+          <t>Anders Haglund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Björndahl</t>
+          <t>Anders Haglund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117770887</v>
+        <v>94158600</v>
       </c>
       <c r="B3" t="n">
-        <v>109957</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,41 +797,57 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hemträsket, Upl</t>
+          <t>Runmarö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716252</v>
+        <v>716241</v>
       </c>
       <c r="R3" t="n">
-        <v>6578277</v>
+        <v>6578274</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,22 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2021-06-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2021-06-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,18 +885,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Haglund</t>
+          <t>Gunnar Björndahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Haglund</t>
+          <t>Gunnar Björndahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -927,12 +907,7 @@
         <v>117770886</v>
       </c>
       <c r="B4" t="n">
-        <v>106856</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31577-2025 artfynd.xlsx
+++ b/artfynd/A 31577-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117770887</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94158600</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,8 +1027,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117770886</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>